--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/مرداد.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/مرداد.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27503"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC9B145-47D0-41AF-A012-A2B656A115D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73816FDB-9F97-4419-8C97-0C5EF2E9E931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="158">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -541,7 +541,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,12 +590,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -624,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -709,12 +703,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -724,10 +712,10 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,30 +1068,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -2701,17 +2689,17 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2839,7 +2827,7 @@
       <c r="E3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="17">
         <v>12200</v>
       </c>
       <c r="G3" s="15">
@@ -2881,7 +2869,7 @@
       <c r="E4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="17">
         <v>13962200</v>
       </c>
       <c r="G4" s="15">
@@ -2921,7 +2909,7 @@
       <c r="E5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="17">
         <v>9000</v>
       </c>
       <c r="G5" s="15">
@@ -2963,7 +2951,7 @@
       <c r="E6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="17">
         <v>2756326</v>
       </c>
       <c r="G6" s="15">
@@ -3003,7 +2991,7 @@
       <c r="E7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="17">
         <v>9000</v>
       </c>
       <c r="G7" s="15">
@@ -3045,7 +3033,7 @@
       <c r="E8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="17">
         <v>1600000</v>
       </c>
       <c r="G8" s="15">
@@ -3085,7 +3073,7 @@
       <c r="E9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="17">
         <v>16480000</v>
       </c>
       <c r="G9" s="15">
@@ -3125,7 +3113,7 @@
       <c r="E10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="17">
         <v>7400000</v>
       </c>
       <c r="G10" s="15">
@@ -3165,7 +3153,7 @@
       <c r="E11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="17">
         <v>18600</v>
       </c>
       <c r="G11" s="15">
@@ -3207,7 +3195,7 @@
       <c r="E12" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="17">
         <v>39318600</v>
       </c>
       <c r="G12" s="15">
@@ -3247,7 +3235,7 @@
       <c r="E13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="17">
         <v>9000</v>
       </c>
       <c r="G13" s="15">
@@ -3289,7 +3277,7 @@
       <c r="E14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="17">
         <v>4000000</v>
       </c>
       <c r="G14" s="15">
@@ -3365,7 +3353,7 @@
       <c r="E16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="17">
         <v>2756000</v>
       </c>
       <c r="G16" s="15">
@@ -3405,7 +3393,7 @@
       <c r="E17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="17">
         <v>1400000</v>
       </c>
       <c r="G17" s="15">
@@ -3481,7 +3469,7 @@
       <c r="E19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="17">
         <v>9000</v>
       </c>
       <c r="G19" s="15">
@@ -3523,7 +3511,7 @@
       <c r="E20" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="17">
         <v>1430000</v>
       </c>
       <c r="G20" s="15">
@@ -3563,7 +3551,7 @@
       <c r="E21" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="17">
         <v>28200</v>
       </c>
       <c r="G21" s="15">
@@ -3605,7 +3593,7 @@
       <c r="E22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="17">
         <v>64500000</v>
       </c>
       <c r="G22" s="15">
@@ -3645,7 +3633,7 @@
       <c r="E23" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="17">
         <v>105000</v>
       </c>
       <c r="G23" s="15">
@@ -3685,7 +3673,7 @@
       <c r="E24" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="17">
         <v>3100000</v>
       </c>
       <c r="G24" s="15">
@@ -3725,7 +3713,7 @@
       <c r="E25" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="17">
         <v>13000000</v>
       </c>
       <c r="G25" s="15">
@@ -3765,7 +3753,7 @@
       <c r="E26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="17">
         <v>2756000</v>
       </c>
       <c r="G26" s="15">
@@ -3841,7 +3829,7 @@
       <c r="E28" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="17">
         <v>16520000</v>
       </c>
       <c r="G28" s="15">
@@ -3881,7 +3869,7 @@
       <c r="E29" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="17">
         <v>2756000</v>
       </c>
       <c r="G29" s="15">
@@ -3993,7 +3981,7 @@
       <c r="E32" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="17">
         <v>31400</v>
       </c>
       <c r="G32" s="15">
@@ -4035,7 +4023,7 @@
       <c r="E33" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="17">
         <v>80000000</v>
       </c>
       <c r="G33" s="15">
@@ -4075,7 +4063,7 @@
       <c r="E34" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="17">
         <v>50340</v>
       </c>
       <c r="G34" s="15">
@@ -4117,7 +4105,7 @@
       <c r="E35" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="17">
         <v>3500000</v>
       </c>
       <c r="G35" s="15">
@@ -4157,7 +4145,7 @@
       <c r="E36" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="17">
         <v>9000</v>
       </c>
       <c r="G36" s="15">
@@ -4199,7 +4187,7 @@
       <c r="E37" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="33">
+      <c r="F37" s="17">
         <v>4000000</v>
       </c>
       <c r="G37" s="15">
@@ -4239,7 +4227,7 @@
       <c r="E38" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="17">
         <v>21500000</v>
       </c>
       <c r="G38" s="15">
@@ -4288,7 +4276,7 @@
       <c r="H39" s="18">
         <v>108861896</v>
       </c>
-      <c r="I39" s="30"/>
+      <c r="I39" s="28"/>
       <c r="J39" s="15"/>
       <c r="K39" s="25">
         <v>192</v>
@@ -4315,7 +4303,7 @@
       <c r="E40" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="F40" s="33">
+      <c r="F40" s="17">
         <v>8099000</v>
       </c>
       <c r="G40" s="15">
@@ -4355,7 +4343,7 @@
       <c r="E41" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="17">
         <v>28200</v>
       </c>
       <c r="G41" s="15">
@@ -4397,7 +4385,7 @@
       <c r="E42" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="17">
         <v>66200000</v>
       </c>
       <c r="G42" s="15">
@@ -4437,7 +4425,7 @@
       <c r="E43" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="33">
+      <c r="F43" s="17">
         <v>559000</v>
       </c>
       <c r="G43" s="15">
@@ -4477,7 +4465,7 @@
       <c r="E44" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="30">
         <v>9000</v>
       </c>
       <c r="G44" s="27">
@@ -4521,7 +4509,7 @@
       <c r="E45" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="30">
         <v>2760000</v>
       </c>
       <c r="G45" s="27">
@@ -4530,7 +4518,7 @@
       <c r="H45" s="27">
         <v>31206696</v>
       </c>
-      <c r="I45" s="31" t="s">
+      <c r="I45" s="29" t="s">
         <v>153</v>
       </c>
       <c r="J45" s="6"/>
@@ -4561,7 +4549,7 @@
       <c r="E46" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="34">
+      <c r="F46" s="30">
         <v>9000</v>
       </c>
       <c r="G46" s="27">
@@ -4605,7 +4593,7 @@
       <c r="E47" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="30">
         <v>4000000</v>
       </c>
       <c r="G47" s="27">
@@ -4614,7 +4602,7 @@
       <c r="H47" s="27">
         <v>27197696</v>
       </c>
-      <c r="I47" s="31" t="s">
+      <c r="I47" s="29" t="s">
         <v>154</v>
       </c>
       <c r="J47" s="6"/>
@@ -4645,7 +4633,7 @@
       <c r="E48" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="30">
         <v>450000</v>
       </c>
       <c r="G48" s="27">
@@ -4654,7 +4642,7 @@
       <c r="H48" s="27">
         <v>26747696</v>
       </c>
-      <c r="I48" s="31" t="s">
+      <c r="I48" s="29" t="s">
         <v>155</v>
       </c>
       <c r="J48" s="6"/>
@@ -4688,7 +4676,7 @@
       <c r="F49" s="27">
         <v>0</v>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="30">
         <v>16000000</v>
       </c>
       <c r="H49" s="27">
@@ -4726,7 +4714,7 @@
       <c r="F50" s="27">
         <v>0</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="30">
         <v>60000000</v>
       </c>
       <c r="H50" s="27">
@@ -4761,7 +4749,7 @@
       <c r="E51" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="30">
         <v>1585000</v>
       </c>
       <c r="G51" s="27">
@@ -4770,7 +4758,7 @@
       <c r="H51" s="27">
         <v>101162696</v>
       </c>
-      <c r="I51" s="31" t="s">
+      <c r="I51" s="29" t="s">
         <v>155</v>
       </c>
       <c r="J51" s="6"/>
@@ -4801,7 +4789,7 @@
       <c r="E52" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F52" s="34">
+      <c r="F52" s="30">
         <v>34600</v>
       </c>
       <c r="G52" s="27">
@@ -4845,7 +4833,7 @@
       <c r="E53" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="30">
         <v>83400000</v>
       </c>
       <c r="G53" s="27">
@@ -4854,7 +4842,7 @@
       <c r="H53" s="27">
         <v>17728096</v>
       </c>
-      <c r="I53" s="31" t="s">
+      <c r="I53" s="29" t="s">
         <v>156</v>
       </c>
       <c r="J53" s="6"/>
@@ -4885,7 +4873,7 @@
       <c r="E54" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="30">
         <v>100000</v>
       </c>
       <c r="G54" s="27">
@@ -4894,7 +4882,7 @@
       <c r="H54" s="27">
         <v>17628096</v>
       </c>
-      <c r="I54" s="31" t="s">
+      <c r="I54" s="29" t="s">
         <v>155</v>
       </c>
       <c r="J54" s="6"/>
@@ -4925,7 +4913,7 @@
       <c r="E55" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="F55" s="34">
+      <c r="F55" s="30">
         <v>9304000</v>
       </c>
       <c r="G55" s="27">
@@ -4934,7 +4922,7 @@
       <c r="H55" s="27">
         <v>8324096</v>
       </c>
-      <c r="I55" s="31" t="s">
+      <c r="I55" s="29" t="s">
         <v>157</v>
       </c>
       <c r="J55" s="6"/>

--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/مرداد.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/مرداد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73816FDB-9F97-4419-8C97-0C5EF2E9E931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CB367C-418A-46A1-ABC0-18623D03B38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4938,7 +4938,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P55" xr:uid="{0335E779-6ADD-4202-996C-586E0AD1A9C0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>